--- a/data/processed/positivacao/2026-05_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2026-05_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -27077,7 +27077,7 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr"/>
@@ -35725,7 +35725,7 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr"/>
@@ -66489,7 +66489,7 @@
     <row r="2546">
       <c r="A2546" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2546" t="inlineStr"/>
@@ -68082,12 +68082,12 @@
       <c r="A2608" t="inlineStr"/>
       <c r="B2608" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 2 cliente(s), não positivou 81 cliente(s) - Total vendido: R$ 4.053,73
+          <t>Vendedor 1 - VENDEDOR 01: positivou 2 cliente(s), não positivou 81 cliente(s) - Total vendido: R$ 4.053,73
 Vendedor 18 - LOJA: positivou 309 cliente(s), não positivou 627 cliente(s) - Total vendido: R$ 94.492,23
-Vendedor 3 - FERNANDA: positivou 3 cliente(s), não positivou 329 cliente(s) - Total vendido: R$ 2.116,60
-Vendedor 4 - DANIELA: positivou 223 cliente(s), não positivou 510 cliente(s) - Total vendido: R$ 188.737,20
+Vendedor 3 - VENDEDOR 03: positivou 3 cliente(s), não positivou 329 cliente(s) - Total vendido: R$ 2.116,60
+Vendedor 4 - VENDEDOR 04: positivou 223 cliente(s), não positivou 510 cliente(s) - Total vendido: R$ 188.737,20
 Vendedor 5 - SITE: positivou 2 cliente(s), não positivou 447 cliente(s) - Total vendido: R$ 452,09
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2608" t="inlineStr"/>
